--- a/TOP埋点治理记录_副本_1.xlsx
+++ b/TOP埋点治理记录_副本_1.xlsx
@@ -7585,7 +7585,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>期望页下一步_期望前置版在APP_C-首善触发时上报，用于记录期望页下一步_期望前置版相关行为。</t>
+          <t>期望前置版期望页曝光后，点击下一步时，上报埋点上报时机：下一步按钮可点击的状态下，点击时就上报 PM：对的，可点击的状态下，点击时就上报</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>tp高搜引导浮层在APP_B-牛人列表-简历详情触发时上报，用于记录tp高搜引导浮层相关行为。</t>
+          <t>1309.252【商业】TP职类在牛人简历页结合ai引导B搜索APP+PC:1309.252【商业】TP职类在牛人简历页结合ai引导B搜索APP+PC@程心宇@高华语</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -7749,7 +7749,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>微简历高亮词在APP_B-牛人列表-简历详情触发时上报，用于记录微简历高亮词相关行为。</t>
+          <t>1309.252【商业】TP职类在牛人简历页结合ai引导B搜索APP+PC:1309.252【商业】TP职类在牛人简历页结合ai引导B搜索APP+PC@程心宇@高华语</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>微简历高亮词在APP_B-牛人列表-简历详情触发时上报，用于记录微简历高亮词相关行为。</t>
+          <t>1309.252【商业】TP职类在牛人简历页结合ai引导B搜索APP+PC:1309.252【商业】TP职类在牛人简历页结合ai引导B搜索APP+PC@程心宇@高华语</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>无页面位置-Ai沟通助手-曝光</t>
+          <t>B_道具_我的道具-Ai沟通助手-曝光</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>无页面位置</t>
+          <t>APP_B-我的-常用功能-招聘道具,Web_B-道具-我的道具</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>Ai沟通助手在服务端场景触发时上报，用于记录Ai沟通助手相关行为。</t>
+          <t>开聊牛人购买成功页的「AI助手开关」曝光（1309.251）购买成功页的「AI助手开关」曝光（1310.243）</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>无页面位置-Ai沟通助手-点击</t>
+          <t>B_道具_我的道具-Ai沟通助手-点击</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>无页面位置</t>
+          <t>APP_B-我的-常用功能-招聘道具,Web_B-道具-我的道具</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8019,7 +8019,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>Ai沟通助手在服务端场景触发时上报，用于记录Ai沟通助手相关行为。</t>
+          <t>搜畅开聊牛人购买成功页点击操作「AI助手开关」（退出弹窗时才上报结果，过程不上报）（1309.251）购买成功页点击操作「AI助手开关」（退出弹窗时才上报结果，过程不上报）（1310.243）</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>无页面位置-Ai沟通助手弹窗-点击</t>
+          <t>B_道具_我的道具-Ai沟通助手弹窗-点击</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>无页面位置</t>
+          <t>APP_B-我的-常用功能-招聘道具,Web_B-道具-我的道具</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>Ai沟通助手弹窗在服务端场景触发时上报，用于记录Ai沟通助手弹窗相关行为。</t>
+          <t>聊天页面中AI助手介绍弹窗点击跳转开关设置（1309.251）</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>无页面位置-聊天框查看Ai沟通助手-点击</t>
+          <t>B_道具_我的道具-聊天框查看Ai沟通助手-点击</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>无页面位置</t>
+          <t>APP_B-我的-常用功能-招聘道具,Web_B-道具-我的道具</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -8207,7 +8207,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>聊天框查看Ai沟通助手在服务端场景触发时上报，用于记录聊天框查看Ai沟通助手相关行为。</t>
+          <t>聊天页面使用AI沟通助手后，聊天窗口点击“立即查看”Ai沟通助手（1309.251）</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>purple屏幕在Web_B-purple触发时上报，用于记录purple屏幕相关行为。</t>
+          <t>每个简历出现在屏幕中时上报注意：必须展开&amp;出现在评估才算曝光才需要上报，折叠状态不需要上报</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>联系牛人在Web_B-purple触发时上报，用于记录联系牛人相关行为。</t>
+          <t>每次点击开聊或点击电话沟通时</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
